--- a/results/Int Task Remove ACC -0.1/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_1_permute.xlsx
@@ -440,797 +440,797 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7415361225294217</v>
+        <v>0.7637412016442366</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7435497494228278</v>
+        <v>0.7644191677459315</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7435497494228278</v>
+        <v>0.755361225294217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7399155357846725</v>
+        <v>0.7543713046905793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7399155357846725</v>
+        <v>0.752635846612985</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7425936145053212</v>
+        <v>0.7492257446928319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7458753308181767</v>
+        <v>0.7535311672954559</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7475026747001521</v>
+        <v>0.7518497663156709</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7471772059237569</v>
+        <v>0.7462762542935977</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7504927079227435</v>
+        <v>0.7496863562137508</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7713350976969424</v>
+        <v>0.7456793738386169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7773286784165776</v>
+        <v>0.7456793738386169</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7604335829720141</v>
+        <v>0.741232051354243</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7850779886254857</v>
+        <v>0.7483506954220396</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7894509826003717</v>
+        <v>0.7591305816768963</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7860611520918971</v>
+        <v>0.7659992116673235</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7860611520918971</v>
+        <v>0.7649619911031027</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7850779886254857</v>
+        <v>0.7649619911031027</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7850779886254857</v>
+        <v>0.7787454248550031</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7876817388366462</v>
+        <v>0.7787454248550031</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7705422602624021</v>
+        <v>0.775660791711245</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7705422602624021</v>
+        <v>0.7771327214370178</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7684137620361506</v>
+        <v>0.7717427783095895</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7584469846275128</v>
+        <v>0.7717427783095895</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7736674362295175</v>
+        <v>0.7717292640351372</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7736674362295175</v>
+        <v>0.7741494453516526</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.77433188805676</v>
+        <v>0.7734512078382791</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.77433188805676</v>
+        <v>0.7666242468607467</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7770369953263134</v>
+        <v>0.7730164986767273</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7760200461737711</v>
+        <v>0.7739996621431386</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7777014471535559</v>
+        <v>0.7880072076130413</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7790844079058505</v>
+        <v>0.8055464834731685</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7767790979221803</v>
+        <v>0.7969840644180415</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7593287910355313</v>
+        <v>0.8081513598738668</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.761681400979785</v>
+        <v>0.8245306605101639</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7684340334478292</v>
+        <v>0.8147271805844923</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7627670476941268</v>
+        <v>0.8110062503519342</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7687932879103553</v>
+        <v>0.777334309364266</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7708271862154401</v>
+        <v>0.8094295849991553</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7808604088068022</v>
+        <v>0.8056737428909286</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7886378737541528</v>
+        <v>0.7701098034799256</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7974784616250915</v>
+        <v>0.7717912044597106</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.798142913452334</v>
+        <v>0.7727878822005743</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8045971056928881</v>
+        <v>0.7735536910862097</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7774807140041669</v>
+        <v>0.7606115209189707</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7774807140041669</v>
+        <v>0.6533825102764795</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.777772397094431</v>
+        <v>0.6060307449743793</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7769930739343431</v>
+        <v>0.6125266062278281</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7595427670476942</v>
+        <v>0.6384244608367589</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7578343375190044</v>
+        <v>0.5985776226138859</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7264710850836196</v>
+        <v>0.6244912438763444</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7300636297088801</v>
+        <v>0.5941978715017737</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6897775775663044</v>
+        <v>0.5488721211779942</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6945897854608931</v>
+        <v>0.566405766090433</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7146787544343713</v>
+        <v>0.5588591699983108</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6956427726786418</v>
+        <v>0.566473337462695</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7012500703868461</v>
+        <v>0.5651376766709837</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6985855059406498</v>
+        <v>0.5290872233796948</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7003074497437918</v>
+        <v>0.5293991778816375</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7270139084407905</v>
+        <v>0.5333723745706402</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6998975167520693</v>
+        <v>0.5271141393096458</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6679531505152316</v>
+        <v>0.5194594290219043</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6676209246016105</v>
+        <v>0.5164626386620869</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6689836139422265</v>
+        <v>0.5164626386620869</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6638245396700264</v>
+        <v>0.516143927022918</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6670184131989414</v>
+        <v>0.5148150233684329</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6536077481840193</v>
+        <v>0.5148150233684329</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6520964018244271</v>
+        <v>0.5071501773748522</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6425023931527676</v>
+        <v>0.5044247986936201</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5961090151472492</v>
+        <v>0.5044247986936201</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5251579480826623</v>
+        <v>0.5013807083732192</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5733216960414438</v>
+        <v>0.5000247761698293</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5573985021679149</v>
+        <v>0.4915231713497382</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5329646939579932</v>
+        <v>0.4897595585337012</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5329646939579932</v>
+        <v>0.4818413198941382</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5543217523509206</v>
+        <v>0.4977870375584211</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5463607185089251</v>
+        <v>0.4981260206092686</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5781789515175404</v>
+        <v>0.4767881074384819</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5781789515175404</v>
+        <v>0.4822456219381722</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.583092516470522</v>
+        <v>0.4822456219381722</v>
       </c>
     </row>
     <row r="82">
@@ -1240,17 +1240,17 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6604133115603357</v>
+        <v>0.4792082887549975</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6143037333183174</v>
+        <v>0.4819471817106819</v>
       </c>
     </row>
     <row r="84">
@@ -1260,67 +1260,67 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5255070668393491</v>
+        <v>0.499640745537474</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5301582296300468</v>
+        <v>0.4999662143138691</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5301582296300468</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5072413987274058</v>
+        <v>0.5003322259136213</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5072413987274058</v>
+        <v>0.5003322259136213</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5026510501717439</v>
+        <v>0.5003322259136213</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4985629821498958</v>
+        <v>0.5003322259136213</v>
       </c>
     </row>
   </sheetData>
